--- a/Demo/MDA/demo_mda_9999_6_supervision_district.xlsx
+++ b/Demo/MDA/demo_mda_9999_6_supervision_district.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D704365-1D77-4FC6-953F-2FF3B81DCF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF0B875-2A98-4C1A-8A48-F42FD193ADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="249">
   <si>
     <t>type</t>
   </si>
@@ -78,12 +78,6 @@
     <t>Recommandations superviseur</t>
   </si>
   <si>
-    <t>geopoint</t>
-  </si>
-  <si>
-    <t>Coordonnées GPS</t>
-  </si>
-  <si>
     <t>list_name</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>s_recommandations</t>
   </si>
   <si>
-    <t>s_gps</t>
-  </si>
-  <si>
     <t>state</t>
   </si>
   <si>
@@ -427,12 +418,6 @@
   </si>
   <si>
     <t>Community.leaders</t>
-  </si>
-  <si>
-    <t>${s_state}</t>
-  </si>
-  <si>
-    <t>${s_district}</t>
   </si>
   <si>
     <t>disease</t>
@@ -558,9 +543,6 @@
     <t>Village</t>
   </si>
   <si>
-    <t>${s_health_facility}</t>
-  </si>
-  <si>
     <t>supervisor</t>
   </si>
   <si>
@@ -594,9 +576,6 @@
     <t>s_med_bag</t>
   </si>
   <si>
-    <t>intger</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
@@ -715,13 +694,97 @@
   </si>
   <si>
     <t>Is the procedure to follow in the event of adverse events known?</t>
+  </si>
+  <si>
+    <t>Misangi</t>
+  </si>
+  <si>
+    <t>Mutoshi</t>
+  </si>
+  <si>
+    <t>Nyabibwe</t>
+  </si>
+  <si>
+    <t>Mwadingusha</t>
+  </si>
+  <si>
+    <t>Kalelu</t>
+  </si>
+  <si>
+    <t>Sange</t>
+  </si>
+  <si>
+    <t>Kimputu</t>
+  </si>
+  <si>
+    <t>Soyo</t>
+  </si>
+  <si>
+    <t>Bwito</t>
+  </si>
+  <si>
+    <t>Kafubu</t>
+  </si>
+  <si>
+    <t>Biakato</t>
+  </si>
+  <si>
+    <t>Hoho</t>
+  </si>
+  <si>
+    <t>Mbujimayi Rural</t>
+  </si>
+  <si>
+    <t>Lubudi</t>
+  </si>
+  <si>
+    <t>Kiyaka</t>
+  </si>
+  <si>
+    <t>Lovo</t>
+  </si>
+  <si>
+    <t>Mavivi</t>
+  </si>
+  <si>
+    <t>Kando</t>
+  </si>
+  <si>
+    <t>Kabondo</t>
+  </si>
+  <si>
+    <t>Kipata</t>
+  </si>
+  <si>
+    <t>s_complete_form</t>
+  </si>
+  <si>
+    <t>s_case_mngt</t>
+  </si>
+  <si>
+    <t>s_has_inegidible</t>
+  </si>
+  <si>
+    <t>s_follow_side_effect</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>state = ${s_state}</t>
+  </si>
+  <si>
+    <t>district = ${s_district}</t>
+  </si>
+  <si>
+    <t>health_facility = ${s_health_facility}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -765,8 +828,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,6 +853,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,7 +891,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -871,6 +948,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1174,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -1188,7 +1268,7 @@
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="17" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1201,60 +1281,60 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="N1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="10"/>
@@ -1273,13 +1353,13 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
@@ -1298,15 +1378,15 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
@@ -1318,8 +1398,8 @@
         <v>7</v>
       </c>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>135</v>
+      <c r="L4" s="16" t="s">
+        <v>246</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1327,15 +1407,15 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
@@ -1347,8 +1427,8 @@
         <v>7</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>136</v>
+      <c r="L5" s="16" t="s">
+        <v>247</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1356,15 +1436,15 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
@@ -1376,8 +1456,8 @@
         <v>7</v>
       </c>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>175</v>
+      <c r="L6" s="21" t="s">
+        <v>248</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1390,10 +1470,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
@@ -1417,10 +1497,10 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
@@ -1441,13 +1521,13 @@
     </row>
     <row r="9" spans="1:21" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>161</v>
-      </c>
       <c r="C9" s="19" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="16"/>
@@ -1472,21 +1552,21 @@
     </row>
     <row r="10" spans="1:21" s="17" customFormat="1" ht="374.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="16"/>
       <c r="F10" s="21" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
@@ -1507,13 +1587,13 @@
     </row>
     <row r="11" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5"/>
@@ -1534,13 +1614,13 @@
     </row>
     <row r="12" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5"/>
@@ -1561,13 +1641,13 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
@@ -1586,13 +1666,13 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
@@ -1600,7 +1680,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1616,10 +1696,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23" t="s">
@@ -1638,15 +1718,15 @@
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5"/>
@@ -1654,7 +1734,9 @@
       <c r="G16" s="6"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="J16" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -1663,15 +1745,15 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5"/>
@@ -1679,7 +1761,9 @@
       <c r="G17" s="6"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="J17" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -1688,15 +1772,15 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5"/>
@@ -1704,7 +1788,9 @@
       <c r="G18" s="6"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="J18" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -1713,15 +1799,15 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
@@ -1729,7 +1815,9 @@
       <c r="G19" s="6"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="J19" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
@@ -1738,7 +1826,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>13</v>
       </c>
@@ -1750,7 +1838,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="J20" s="10"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -1759,15 +1847,15 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
@@ -1775,7 +1863,9 @@
       <c r="G21" s="6"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="J21" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -1784,25 +1874,27 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="J22" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
@@ -1811,15 +1903,15 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
@@ -1827,7 +1919,9 @@
       <c r="G23" s="6"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="J23" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
@@ -1836,15 +1930,15 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
@@ -1852,7 +1946,9 @@
       <c r="G24" s="6"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="J24" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
@@ -1861,13 +1957,15 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>241</v>
+      </c>
       <c r="C25" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
@@ -1875,7 +1973,9 @@
       <c r="G25" s="6"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="J25" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -1884,13 +1984,15 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>242</v>
+      </c>
       <c r="C26" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
@@ -1898,7 +2000,9 @@
       <c r="G26" s="6"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="J26" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -1907,13 +2011,15 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>243</v>
+      </c>
       <c r="C27" s="6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
@@ -1921,7 +2027,9 @@
       <c r="G27" s="6"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="J27" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -1930,13 +2038,15 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="C28" s="6" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
@@ -1944,7 +2054,9 @@
       <c r="G28" s="6"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="J28" s="10" t="s">
+        <v>7</v>
+      </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -1974,17 +2086,23 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="6"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="J30" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
@@ -1998,10 +2116,10 @@
         <v>14</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
@@ -2025,10 +2143,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
@@ -2048,24 +2166,16 @@
       <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="6"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
@@ -2076,23 +2186,19 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>19</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
@@ -2103,10 +2209,10 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -2124,29 +2230,6 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2154,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -2164,28 +2247,36 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -2194,13 +2285,13 @@
     </row>
     <row r="3" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
@@ -2209,13 +2300,13 @@
     </row>
     <row r="4" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
@@ -2224,13 +2315,13 @@
     </row>
     <row r="5" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2248,13 +2339,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2263,13 +2354,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -2278,13 +2369,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -2293,13 +2384,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -2308,13 +2399,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -2323,13 +2414,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -2347,13 +2438,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -2362,13 +2453,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2377,13 +2468,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -2392,13 +2483,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -2407,13 +2498,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -2431,13 +2522,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -2446,13 +2537,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -2461,13 +2552,13 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -2476,13 +2567,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -2491,13 +2582,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -2515,13 +2606,13 @@
     </row>
     <row r="26" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
@@ -2530,13 +2621,13 @@
     </row>
     <row r="27" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -2545,13 +2636,13 @@
     </row>
     <row r="28" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -2560,13 +2651,13 @@
     </row>
     <row r="29" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
@@ -2575,13 +2666,13 @@
     </row>
     <row r="30" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>142</v>
-      </c>
       <c r="C30" s="19" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
@@ -2599,112 +2690,112 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C36" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C39" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
@@ -2713,13 +2804,13 @@
     </row>
     <row r="43" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
@@ -2728,13 +2819,13 @@
     </row>
     <row r="44" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
@@ -2743,13 +2834,13 @@
     </row>
     <row r="45" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
@@ -2758,13 +2849,13 @@
     </row>
     <row r="46" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>148</v>
-      </c>
       <c r="C46" s="19" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
@@ -2773,13 +2864,13 @@
     </row>
     <row r="47" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
@@ -2788,13 +2879,13 @@
     </row>
     <row r="48" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
@@ -2803,13 +2894,13 @@
     </row>
     <row r="49" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
@@ -2818,13 +2909,13 @@
     </row>
     <row r="50" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
@@ -2833,13 +2924,13 @@
     </row>
     <row r="51" spans="1:7" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
@@ -2857,13 +2948,13 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2872,13 +2963,13 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2887,13 +2978,13 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="C55" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2902,13 +2993,13 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2917,13 +3008,13 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2932,13 +3023,13 @@
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2947,13 +3038,13 @@
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
@@ -2962,13 +3053,13 @@
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -2977,13 +3068,13 @@
     </row>
     <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -2992,13 +3083,13 @@
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
@@ -3019,13 +3110,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
@@ -3036,13 +3127,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
@@ -3053,13 +3144,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
@@ -3070,13 +3161,13 @@
         <v>8</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
@@ -3087,13 +3178,13 @@
         <v>8</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
@@ -3104,13 +3195,13 @@
         <v>8</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
@@ -3121,13 +3212,13 @@
         <v>8</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
@@ -3138,13 +3229,13 @@
         <v>8</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
@@ -3155,13 +3246,13 @@
         <v>8</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
@@ -3172,13 +3263,13 @@
         <v>8</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
@@ -3189,13 +3280,13 @@
         <v>8</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
@@ -3206,13 +3297,13 @@
         <v>8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -3223,13 +3314,13 @@
         <v>8</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
@@ -3240,13 +3331,13 @@
         <v>8</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
@@ -3257,13 +3348,13 @@
         <v>8</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
@@ -3274,13 +3365,13 @@
         <v>8</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
@@ -3291,13 +3382,13 @@
         <v>8</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
@@ -3308,13 +3399,13 @@
         <v>8</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
@@ -3325,13 +3416,13 @@
         <v>8</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
@@ -3342,13 +3433,13 @@
         <v>8</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
@@ -3365,343 +3456,683 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D85" s="5"/>
       <c r="E85" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="C87" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D87" s="5"/>
       <c r="E87" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D93" s="5"/>
       <c r="E93" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G106" s="5"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G107" s="5"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G108" s="5"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G109" s="5"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G110" s="5"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G111" s="5"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G112" s="5"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G113" s="5"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G114" s="5"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G115" s="5"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G116" s="5"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G117" s="5"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G118" s="5"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C119" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G119" s="5"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G120" s="5"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C121" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G121" s="5"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C122" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G122" s="5"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C123" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G123" s="5"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G124" s="5"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C125" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G125" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3721,25 +4152,25 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
